--- a/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
+++ b/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
+++ b/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
+++ b/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
+++ b/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
+++ b/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3190" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
     <t>0</t>
@@ -527,14 +530,24 @@
     <t>http://hl7.org/fhir/ValueSet/condition-clinical|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>con-3
+con-4con-5</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>&lt; 303105007 |Disease phases|</t>
+  </si>
+  <si>
+    <t>PRB-14</t>
+  </si>
+  <si>
+    <t>Observation ACT
+.inboundRelationship[typeCode=COMP].source[classCode=OBS, code="clinicalStatus", moodCode=EVN].value</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
   </si>
   <si>
     <t>Condition.verificationStatus</t>
@@ -552,6 +565,23 @@
     <t>http://hl7.org/fhir/ValueSet/condition-ver-status|4.0.1</t>
   </si>
   <si>
+    <t>con-3
+con-5</t>
+  </si>
+  <si>
+    <t>&lt; 410514004 |Finding context value|</t>
+  </si>
+  <si>
+    <t>PRB-13</t>
+  </si>
+  <si>
+    <t>Observation ACT
+.inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
+  </si>
+  <si>
+    <t>408729009</t>
+  </si>
+  <si>
     <t>Condition.category</t>
   </si>
   <si>
@@ -571,6 +601,18 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+  </si>
+  <si>
+    <t>&lt; 404684003 |Clinical finding|</t>
+  </si>
+  <si>
+    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
   </si>
   <si>
     <t>Condition.category.id</t>
@@ -633,10 +675,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
   </si>
   <si>
     <t>Condition.category.coding.id</t>
@@ -817,6 +859,21 @@
     <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
   </si>
   <si>
+    <t>&lt; 272141005 |Severities|</t>
+  </si>
+  <si>
+    <t>PRB-26 / ABS-3</t>
+  </si>
+  <si>
+    <t>Can be pre/post-coordinated into value.  Or ./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="severity"].value</t>
+  </si>
+  <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
+    <t>246112005</t>
+  </si>
+  <si>
     <t>Condition.code</t>
   </si>
   <si>
@@ -827,9 +884,6 @@
     <t>病情、問題或診斷的識別</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>0..1，主要用於說明敘述性resource。</t>
   </si>
   <si>
@@ -840,6 +894,33 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>code 246090004 |Associated finding| (&lt; 404684003 |Clinical finding| MINUS
+&lt;&lt; 420134006 |Propensity to adverse reactions| MINUS 
+&lt;&lt; 473010000 |Hypersensitivity condition| MINUS 
+&lt;&lt; 79899007 |Drug interaction| MINUS
+&lt;&lt; 69449002 |Drug action| MINUS 
+&lt;&lt; 441742003 |Evaluation finding| MINUS 
+&lt;&lt; 307824009 |Administrative status| MINUS 
+&lt;&lt; 385356007 |Tumor stage finding|) 
+OR &lt; 413350009 |Finding with explicit context|
+OR &lt; 272379006 |Event|</t>
+  </si>
+  <si>
+    <t>PRB-3</t>
+  </si>
+  <si>
+    <t>.value</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>246090004</t>
   </si>
   <si>
     <t>Condition.code.id</t>
@@ -1014,6 +1095,15 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
+  </si>
+  <si>
+    <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
+  </si>
+  <si>
+    <t>.targetBodySiteCode</t>
+  </si>
+  <si>
+    <t>363698007</t>
   </si>
   <si>
     <t>Condition.subject</t>
@@ -1377,6 +1467,13 @@
     <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
   </si>
   <si>
+    <t xml:space="preserve">con-1
+</t>
+  </si>
+  <si>
+    <t>&lt; 254291000 |Staging and scales|</t>
+  </si>
+  <si>
     <t>Condition.stage.assessment</t>
   </si>
   <si>
@@ -1390,10 +1487,6 @@
     <t>分期評估所依據的證據之正式記錄</t>
   </si>
   <si>
-    <t xml:space="preserve">con-1
-</t>
-  </si>
-  <si>
     <t>.self</t>
   </si>
   <si>
@@ -1410,6 +1503,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+  </si>
+  <si>
+    <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
   </si>
   <si>
     <t>Condition.evidence</t>
@@ -1455,24 +1551,30 @@
     <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
   </si>
   <si>
-    <t>Condition.evidence.detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
-    <t>在其他地方找到的支持資訊</t>
-  </si>
-  <si>
-    <t>其他相關資訊的連接，包括病理報告。</t>
-  </si>
-  <si>
     <t xml:space="preserve">con-2
 </t>
   </si>
   <si>
+    <t>Event.reasonCode</t>
+  </si>
+  <si>
+    <t>[code="diagnosis"].value</t>
+  </si>
+  <si>
     <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>Condition.evidence.detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>在其他地方找到的支持資訊</t>
+  </si>
+  <si>
+    <t>其他相關資訊的連接，包括病理報告。</t>
   </si>
   <si>
     <t>Condition.note</t>
@@ -1811,7 +1913,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO85"/>
+  <dimension ref="A1:AP85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.99609375" customWidth="true" bestFit="true"/>
@@ -1851,9 +1953,10 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="58.4765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="190.4140625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1980,6 +2083,9 @@
       <c r="AO1" t="s" s="1">
         <v>77</v>
       </c>
+      <c r="AP1" t="s" s="1">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1994,10 +2100,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2009,13 +2115,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -2069,39 +2175,42 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2109,10 +2218,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2121,19 +2230,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2183,13 +2292,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2210,15 +2319,18 @@
         <v>20</v>
       </c>
       <c r="AO3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2226,10 +2338,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2238,16 +2350,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2298,19 +2410,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2325,15 +2437,18 @@
         <v>20</v>
       </c>
       <c r="AO4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2341,31 +2456,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2415,19 +2530,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2442,15 +2557,18 @@
         <v>20</v>
       </c>
       <c r="AO5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2458,10 +2576,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2473,16 +2591,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2496,7 +2614,7 @@
         <v>20</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U6" t="s" s="2">
         <v>20</v>
@@ -2508,13 +2626,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2532,19 +2650,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2559,26 +2677,29 @@
         <v>20</v>
       </c>
       <c r="AO6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2590,16 +2711,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2649,19 +2770,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2673,29 +2794,32 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2707,16 +2831,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2766,13 +2890,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2790,29 +2914,32 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2824,16 +2951,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2883,19 +3010,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2907,53 +3034,56 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -3002,19 +3132,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3026,18 +3156,21 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3045,10 +3178,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -3057,22 +3190,22 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3121,22 +3254,22 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
@@ -3145,18 +3278,21 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="AP11" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3164,31 +3300,31 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3214,13 +3350,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -3238,42 +3374,45 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AO12" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3281,31 +3420,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3331,66 +3470,69 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z13" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AA13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
+      </c>
+      <c r="AP13" t="s" s="2">
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3398,13 +3540,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>20</v>
@@ -3413,16 +3555,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3448,13 +3590,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3472,42 +3614,45 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3515,10 +3660,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3530,13 +3675,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3587,13 +3732,13 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -3611,18 +3756,21 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3630,10 +3778,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3645,13 +3793,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3690,31 +3838,31 @@
         <v>20</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -3729,15 +3877,18 @@
         <v>20</v>
       </c>
       <c r="AO16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3745,34 +3896,34 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3821,19 +3972,19 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3842,21 +3993,24 @@
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3864,10 +4018,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3879,13 +4033,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3936,13 +4090,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3960,18 +4114,21 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3979,10 +4136,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3994,16 +4151,16 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4041,31 +4198,31 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -4080,15 +4237,18 @@
         <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4096,34 +4256,34 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4133,7 +4293,7 @@
         <v>20</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>20</v>
@@ -4172,19 +4332,19 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
@@ -4193,21 +4353,24 @@
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="AO20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4215,10 +4378,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4227,19 +4390,19 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4289,19 +4452,19 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -4310,21 +4473,24 @@
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="AO21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4332,32 +4498,32 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4367,7 +4533,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -4406,19 +4572,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4427,21 +4593,24 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4449,32 +4618,32 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4523,19 +4692,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4544,21 +4713,24 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4566,10 +4738,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4578,22 +4750,22 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4642,19 +4814,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4663,21 +4835,24 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="AO24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4685,34 +4860,34 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4761,19 +4936,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4782,21 +4957,24 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4804,13 +4982,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4819,16 +4997,16 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4854,13 +5032,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4878,77 +5056,78 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>165</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>166</v>
+        <v>274</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>20</v>
+        <v>275</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>276</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4973,13 +5152,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4997,42 +5176,45 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>20</v>
+        <v>284</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>165</v>
+        <v>286</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>166</v>
+        <v>287</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>289</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5040,10 +5222,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5055,13 +5237,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5112,13 +5294,13 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
@@ -5136,18 +5318,21 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5155,10 +5340,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5170,13 +5355,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5215,31 +5400,31 @@
         <v>20</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5254,15 +5439,18 @@
         <v>20</v>
       </c>
       <c r="AO29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5270,34 +5458,34 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5334,29 +5522,29 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5365,58 +5553,61 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5441,11 +5632,11 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5463,19 +5654,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5484,58 +5675,61 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5560,13 +5754,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5584,19 +5778,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5605,58 +5799,61 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5681,13 +5878,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5705,19 +5902,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5726,58 +5923,61 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5802,11 +6002,11 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5824,19 +6024,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5845,58 +6045,61 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5921,13 +6124,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5945,19 +6148,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5966,58 +6169,61 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6042,13 +6248,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6066,19 +6272,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6087,58 +6293,61 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6148,7 +6357,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -6187,19 +6396,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -6208,21 +6417,24 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AO37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6230,10 +6442,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6245,13 +6457,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6302,13 +6514,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -6326,18 +6538,21 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6345,10 +6560,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6360,16 +6575,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6407,31 +6622,31 @@
         <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6446,15 +6661,18 @@
         <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6462,34 +6680,34 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6499,7 +6717,7 @@
         <v>20</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>20</v>
@@ -6538,19 +6756,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6559,21 +6777,24 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="AO40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6581,10 +6802,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6593,19 +6814,19 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6655,19 +6876,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6676,21 +6897,24 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6698,32 +6922,32 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6772,19 +6996,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -6793,21 +7017,24 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="AO42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6815,32 +7042,32 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6889,19 +7116,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -6910,21 +7137,24 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="AO43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6932,10 +7162,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6944,22 +7174,22 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7008,19 +7238,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7029,21 +7259,24 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="AO44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7051,34 +7284,34 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7127,19 +7360,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7148,21 +7381,24 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="AO45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7170,31 +7406,31 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7220,13 +7456,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7244,75 +7480,78 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>166</v>
+        <v>348</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>349</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7361,42 +7600,45 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>333</v>
+        <v>359</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7404,10 +7646,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7419,13 +7661,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7476,13 +7718,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -7500,29 +7742,32 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7534,16 +7779,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7581,31 +7826,31 @@
         <v>20</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7617,18 +7862,21 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7636,31 +7884,31 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7710,19 +7958,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -7734,18 +7982,21 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7753,10 +8004,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7765,19 +8016,19 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7803,13 +8054,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7827,19 +8078,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7851,18 +8102,21 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7870,10 +8124,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7882,19 +8136,19 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7944,19 +8198,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -7968,18 +8222,21 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="AO52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7987,10 +8244,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7999,19 +8256,19 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8061,19 +8318,19 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8085,18 +8342,21 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8104,10 +8364,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8116,19 +8376,19 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8178,42 +8438,45 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>371</v>
+        <v>397</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8221,31 +8484,31 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8295,42 +8558,45 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>380</v>
+        <v>406</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8338,13 +8604,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
@@ -8353,16 +8619,16 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8412,19 +8678,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8436,18 +8702,21 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>387</v>
+        <v>413</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8455,10 +8724,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8467,16 +8736,16 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8527,19 +8796,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8548,21 +8817,24 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>394</v>
+        <v>420</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8570,28 +8842,28 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8642,19 +8914,19 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
@@ -8666,18 +8938,21 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>400</v>
+        <v>426</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8685,10 +8960,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8700,13 +8975,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8757,13 +9032,13 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
@@ -8781,29 +9056,32 @@
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -8815,16 +9093,16 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8862,31 +9140,31 @@
         <v>20</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -8898,18 +9176,21 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8917,31 +9198,31 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8991,19 +9272,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9015,18 +9296,21 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9034,10 +9318,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9046,19 +9330,19 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9084,13 +9368,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9108,19 +9392,19 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
@@ -9132,18 +9416,21 @@
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9151,10 +9438,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9163,19 +9450,19 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9225,19 +9512,19 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9249,18 +9536,21 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9268,10 +9558,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9280,19 +9570,19 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9342,19 +9632,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9366,18 +9656,21 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9385,28 +9678,28 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9457,19 +9750,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -9478,21 +9771,24 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>413</v>
+        <v>439</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9500,10 +9796,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -9515,13 +9811,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9572,13 +9868,13 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
@@ -9596,29 +9892,32 @@
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9630,16 +9929,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9677,31 +9976,31 @@
         <v>20</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -9713,18 +10012,21 @@
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9732,31 +10034,31 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9806,19 +10108,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -9830,18 +10132,21 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9849,10 +10154,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -9861,19 +10166,19 @@
         <v>20</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9899,13 +10204,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9923,19 +10228,19 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -9947,18 +10252,21 @@
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9966,10 +10274,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -9978,19 +10286,19 @@
         <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10040,19 +10348,19 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -10064,18 +10372,21 @@
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10083,10 +10394,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10095,19 +10406,19 @@
         <v>20</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10157,19 +10468,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10181,18 +10492,21 @@
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10200,10 +10514,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -10215,13 +10529,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10272,19 +10586,19 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -10296,18 +10610,21 @@
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10315,10 +10632,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10330,13 +10647,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10387,13 +10704,13 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
@@ -10411,29 +10728,32 @@
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -10445,16 +10765,16 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10504,19 +10824,19 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -10528,53 +10848,56 @@
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -10623,19 +10946,19 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
@@ -10647,18 +10970,21 @@
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10666,10 +10992,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -10681,17 +11007,15 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -10716,13 +11040,13 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -10740,42 +11064,45 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>164</v>
+        <v>465</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>20</v>
+        <v>466</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>166</v>
+        <v>287</v>
       </c>
       <c r="AO76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10783,10 +11110,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -10798,13 +11125,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10855,19 +11182,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -10879,18 +11206,21 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="AO77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10898,10 +11228,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
@@ -10913,17 +11243,15 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -10948,13 +11276,13 @@
         <v>20</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>20</v>
@@ -10972,19 +11300,19 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -10993,21 +11321,24 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>166</v>
+        <v>477</v>
       </c>
       <c r="AO78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11015,10 +11346,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -11030,16 +11361,16 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11089,19 +11420,19 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -11113,18 +11444,21 @@
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="AO79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11132,10 +11466,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -11147,13 +11481,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11204,13 +11538,13 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
@@ -11228,29 +11562,32 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP80" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -11262,16 +11599,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11321,19 +11658,19 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
@@ -11345,53 +11682,56 @@
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AO81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11440,19 +11780,19 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
@@ -11464,18 +11804,21 @@
         <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11483,10 +11826,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -11495,20 +11838,18 @@
         <v>20</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -11533,13 +11874,13 @@
         <v>20</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -11557,42 +11898,45 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>164</v>
+        <v>492</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>166</v>
+        <v>494</v>
       </c>
       <c r="AO83" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11600,10 +11944,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -11612,16 +11956,16 @@
         <v>20</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11672,19 +12016,19 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
@@ -11696,18 +12040,21 @@
         <v>20</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>469</v>
+        <v>495</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11715,13 +12062,13 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>20</v>
@@ -11730,13 +12077,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11787,38 +12134,41 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="AO85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO85">
+  <autoFilter ref="A1:AP85">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
+++ b/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
+++ b/docs/StructureDefinition-PASportConditionExerciseHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
